--- a/data/ready_stocks/logos-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-wb-stocks-updated.xlsx
@@ -397,10 +397,883 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:B109"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Баркод</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Количество</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2048684329794</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2048684329817</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2048684329862</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2048684329886</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2048684329909</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2048684329930</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2048684329961</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2048684329992</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2048684330028</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2048684330073</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2048684330097</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2048684330127</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2048684330141</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2048684330158</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2048684330196</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2048684330202</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2048684330240</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2048684330271</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2048684330691</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2048684330721</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2048684330752</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>2048684330776</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2048684330806</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>2048684330844</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>2048684330899</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>2048684330943</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>2048684330974</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>2048684331018</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>2048684331025</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2048684331032</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>2048684331360</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>2048684331391</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>2048684331407</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>2048684331414</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>2048684331421</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>2048684331476</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>2048684331506</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2048684331520</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>2048684331544</v>
+      </c>
+      <c r="B40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>2048684331568</v>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>2048684331575</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2048684331605</v>
+      </c>
+      <c r="B43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2048684331629</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2048684331704</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2048684331766</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2048684331827</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2048684331889</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2048684331919</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2048684331940</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2048684331964</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>2048684331988</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>2048684332008</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>2048684332015</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>2048684332022</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>2048684332046</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2048684332060</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2048684332077</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>2048684332091</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>2048684332114</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>2048684332121</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>2048684328476</v>
+      </c>
+      <c r="B62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>2048684328490</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>2048684328506</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>2048684328513</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>2048684328520</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>2048684328551</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>2048684328568</v>
+      </c>
+      <c r="B68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>2048684328575</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>2048684328582</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>2048684328605</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>2048684328612</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>2048684328636</v>
+      </c>
+      <c r="B73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>2048684328643</v>
+      </c>
+      <c r="B74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>2048684328650</v>
+      </c>
+      <c r="B75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>2048684328674</v>
+      </c>
+      <c r="B76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>2048684328698</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>2048684328728</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>2048684328735</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>2048684328759</v>
+      </c>
+      <c r="B80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>2048684328773</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>2048684328780</v>
+      </c>
+      <c r="B82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>2048684328803</v>
+      </c>
+      <c r="B83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>2048684328810</v>
+      </c>
+      <c r="B84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>2048684328834</v>
+      </c>
+      <c r="B85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>2048684328841</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>2048684328858</v>
+      </c>
+      <c r="B87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>2048684328865</v>
+      </c>
+      <c r="B88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>2048684328872</v>
+      </c>
+      <c r="B89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>2048684328896</v>
+      </c>
+      <c r="B90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>2048684328919</v>
+      </c>
+      <c r="B91">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>2048684329183</v>
+      </c>
+      <c r="B92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>2048684329190</v>
+      </c>
+      <c r="B93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>2048684329206</v>
+      </c>
+      <c r="B94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>2048684329275</v>
+      </c>
+      <c r="B95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>2048684329329</v>
+      </c>
+      <c r="B96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>2048684329343</v>
+      </c>
+      <c r="B97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>2048684329350</v>
+      </c>
+      <c r="B98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>2048684329374</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>2048684329411</v>
+      </c>
+      <c r="B100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>2048684329459</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>2048684329497</v>
+      </c>
+      <c r="B102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>2048684329510</v>
+      </c>
+      <c r="B103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>2048684329527</v>
+      </c>
+      <c r="B104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>2048684329541</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>2048684329558</v>
+      </c>
+      <c r="B106">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>2048729432823</v>
+      </c>
+      <c r="B107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>2048729432861</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>2048729432854</v>
+      </c>
+      <c r="B109">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/logos-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-wb-stocks-updated.xlsx
@@ -436,7 +436,7 @@
         <v>2048684329886</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1084,7 +1084,7 @@
         <v>2048684328841</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -1204,7 +1204,7 @@
         <v>2048684329459</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">

--- a/data/ready_stocks/logos-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:B133"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2048684329794</v>
+        <v>2048684329817</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -417,7 +417,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2048684329817</v>
+        <v>2048684329862</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -425,7 +425,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2048684329862</v>
+        <v>2048684329886</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -433,15 +433,15 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2048684329886</v>
+        <v>2048684329909</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2048684329909</v>
+        <v>2048684329930</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -449,15 +449,15 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>2048684329930</v>
+        <v>2048684329961</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2048684329961</v>
+        <v>2048684329992</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -465,7 +465,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2048684329992</v>
+        <v>2048684330028</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -473,7 +473,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>2048684330028</v>
+        <v>2048684330073</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -481,7 +481,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>2048684330073</v>
+        <v>2048684330097</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -489,7 +489,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2048684330097</v>
+        <v>2048684330127</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>2048684330127</v>
+        <v>2048684330141</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>2048684330141</v>
+        <v>2048684330158</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>2048684330158</v>
+        <v>2048684330196</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>2048684330196</v>
+        <v>2048684330202</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>2048684330202</v>
+        <v>2048684330240</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>2048684330240</v>
+        <v>2048684330271</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -545,15 +545,15 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>2048684330271</v>
+        <v>2048684330691</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>2048684330691</v>
+        <v>2048684330721</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -561,15 +561,15 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>2048684330721</v>
+        <v>2048684330752</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>2048684330752</v>
+        <v>2048684330776</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>2048684330776</v>
+        <v>2048684330806</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>2048684330806</v>
+        <v>2048684330844</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2048684330844</v>
+        <v>2048684330899</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>2048684330899</v>
+        <v>2048684330943</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>2048684330943</v>
+        <v>2048684330974</v>
       </c>
       <c r="B27">
         <v>5</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>2048684330974</v>
+        <v>2048684331018</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>2048684331018</v>
+        <v>2048684331025</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>2048684331025</v>
+        <v>2048684331032</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>2048684331032</v>
+        <v>2048684331360</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -649,15 +649,15 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>2048684331360</v>
+        <v>2048684331391</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>2048684331391</v>
+        <v>2048684331407</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>2048684331407</v>
+        <v>2048684331414</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>2048684331414</v>
+        <v>2048684331421</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -681,23 +681,23 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>2048684331421</v>
+        <v>2048684331476</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2048684331476</v>
+        <v>2048684331506</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2048684331506</v>
+        <v>2048684331520</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>2048684331520</v>
+        <v>2048684331544</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>2048684331544</v>
+        <v>2048684331568</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>2048684331568</v>
+        <v>2048684331575</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2048684331575</v>
+        <v>2048684331605</v>
       </c>
       <c r="B42">
         <v>5</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>2048684331605</v>
+        <v>2048684331629</v>
       </c>
       <c r="B43">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2048684331629</v>
+        <v>2048684331704</v>
       </c>
       <c r="B44">
         <v>5</v>
@@ -753,23 +753,23 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2048684331704</v>
+        <v>2048684331766</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2048684331766</v>
+        <v>2048684331827</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2048684331827</v>
+        <v>2048684331889</v>
       </c>
       <c r="B47">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2048684331889</v>
+        <v>2048684331919</v>
       </c>
       <c r="B48">
         <v>5</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2048684331919</v>
+        <v>2048684331940</v>
       </c>
       <c r="B49">
         <v>5</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2048684331940</v>
+        <v>2048684331964</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2048684331964</v>
+        <v>2048684331988</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>2048684331988</v>
+        <v>2048684332008</v>
       </c>
       <c r="B52">
         <v>5</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>2048684332008</v>
+        <v>2048684332015</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>2048684332015</v>
+        <v>2048684332022</v>
       </c>
       <c r="B54">
         <v>5</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>2048684332022</v>
+        <v>2048684332046</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>2048684332046</v>
+        <v>2048684332060</v>
       </c>
       <c r="B56">
         <v>5</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>2048684332060</v>
+        <v>2048684332077</v>
       </c>
       <c r="B57">
         <v>5</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>2048684332077</v>
+        <v>2048684332091</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>2048684332091</v>
+        <v>2048684332114</v>
       </c>
       <c r="B59">
         <v>5</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>2048684332114</v>
+        <v>2048684332121</v>
       </c>
       <c r="B60">
         <v>5</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>2048684332121</v>
+        <v>2048684328476</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -889,31 +889,31 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>2048684328476</v>
+        <v>2048684328490</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>2048684328490</v>
+        <v>2048684328506</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>2048684328506</v>
+        <v>2048684328513</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>2048684328513</v>
+        <v>2048684328520</v>
       </c>
       <c r="B65">
         <v>5</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>2048684328520</v>
+        <v>2048684328551</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>2048684328551</v>
+        <v>2048684328568</v>
       </c>
       <c r="B67">
         <v>5</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>2048684328568</v>
+        <v>2048684328575</v>
       </c>
       <c r="B68">
         <v>5</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>2048684328575</v>
+        <v>2048684328582</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>2048684328582</v>
+        <v>2048684328605</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -961,15 +961,15 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>2048684328605</v>
+        <v>2048684328612</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>2048684328612</v>
+        <v>2048684328636</v>
       </c>
       <c r="B72">
         <v>5</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>2048684328636</v>
+        <v>2048684328643</v>
       </c>
       <c r="B73">
         <v>5</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>2048684328643</v>
+        <v>2048684328650</v>
       </c>
       <c r="B74">
         <v>5</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>2048684328650</v>
+        <v>2048684328674</v>
       </c>
       <c r="B75">
         <v>5</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>2048684328674</v>
+        <v>2048684328698</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>2048684328698</v>
+        <v>2048684328728</v>
       </c>
       <c r="B77">
         <v>5</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>2048684328728</v>
+        <v>2048684328735</v>
       </c>
       <c r="B78">
         <v>5</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>2048684328735</v>
+        <v>2048684328759</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>2048684328759</v>
+        <v>2048684328773</v>
       </c>
       <c r="B80">
         <v>5</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>2048684328773</v>
+        <v>2048684328780</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>2048684328780</v>
+        <v>2048684328803</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>2048684328803</v>
+        <v>2048684328810</v>
       </c>
       <c r="B83">
         <v>5</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>2048684328810</v>
+        <v>2048684328834</v>
       </c>
       <c r="B84">
         <v>5</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>2048684328834</v>
+        <v>2048684328841</v>
       </c>
       <c r="B85">
         <v>5</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>2048684328841</v>
+        <v>2048684328858</v>
       </c>
       <c r="B86">
         <v>5</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>2048684328858</v>
+        <v>2048684328865</v>
       </c>
       <c r="B87">
         <v>5</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>2048684328865</v>
+        <v>2048684328872</v>
       </c>
       <c r="B88">
         <v>5</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>2048684328872</v>
+        <v>2048684328896</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>2048684328896</v>
+        <v>2048684328919</v>
       </c>
       <c r="B90">
         <v>5</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>2048684328919</v>
+        <v>2048684329183</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>2048684329183</v>
+        <v>2048684329190</v>
       </c>
       <c r="B92">
         <v>5</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>2048684329190</v>
+        <v>2048684329206</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>2048684329206</v>
+        <v>2048684329275</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>2048684329275</v>
+        <v>2048684329329</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>2048684329329</v>
+        <v>2048684329343</v>
       </c>
       <c r="B96">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>2048684329343</v>
+        <v>2048684329350</v>
       </c>
       <c r="B97">
         <v>5</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>2048684329350</v>
+        <v>2048684329374</v>
       </c>
       <c r="B98">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>2048684329374</v>
+        <v>2048684329411</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>2048684329411</v>
+        <v>2048684329459</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>2048684329459</v>
+        <v>2048684329497</v>
       </c>
       <c r="B101">
         <v>5</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>2048684329497</v>
+        <v>2048684329510</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>2048684329510</v>
+        <v>2048684329527</v>
       </c>
       <c r="B103">
         <v>5</v>
@@ -1225,23 +1225,23 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>2048684329527</v>
+        <v>2048684329541</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>2048684329541</v>
+        <v>2048684329558</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>2048684329558</v>
+        <v>2048729432823</v>
       </c>
       <c r="B106">
         <v>5</v>
@@ -1249,31 +1249,223 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>2048729432823</v>
+        <v>2048729432861</v>
       </c>
       <c r="B107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>2048729432861</v>
+        <v>2048729432854</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>2048729432854</v>
+        <v>2048208983624</v>
       </c>
       <c r="B109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>2047914434871</v>
+      </c>
+      <c r="B110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>2047914434864</v>
+      </c>
+      <c r="B111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>2047914434819</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>2047914434727</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>2047914434697</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>2047914434673</v>
+      </c>
+      <c r="B115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>2047914434833</v>
+      </c>
+      <c r="B116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>2047914434840</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>2047914434680</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>2047914434895</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>2049626027266</v>
+      </c>
+      <c r="B120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>2047914434888</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>2047914434758</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>2047914434765</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>2047914434772</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>2047914434734</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>2049627411606</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>2048589156259</v>
+      </c>
+      <c r="B127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>2048589156242</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>2048589156266</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>2047914434703</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>2048589156273</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>2048208983662</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>2048208983587</v>
+      </c>
+      <c r="B133">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B133"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/logos-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/logos-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B134"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2048684329817</v>
+        <v>2048684329794</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -417,7 +417,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2048684329862</v>
+        <v>2048684329817</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -425,7 +425,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2048684329886</v>
+        <v>2048684329862</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -433,15 +433,15 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2048684329909</v>
+        <v>2048684329886</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2048684329930</v>
+        <v>2048684329909</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>2048684329961</v>
+        <v>2048684329930</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>2048684329992</v>
+        <v>2048684329961</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -465,7 +465,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2048684330028</v>
+        <v>2048684329992</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -473,7 +473,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>2048684330073</v>
+        <v>2048684330028</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -481,7 +481,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>2048684330097</v>
+        <v>2048684330073</v>
       </c>
       <c r="B11">
         <v>5</v>
@@ -489,7 +489,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2048684330127</v>
+        <v>2048684330097</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>2048684330141</v>
+        <v>2048684330127</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>2048684330158</v>
+        <v>2048684330141</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>2048684330196</v>
+        <v>2048684330158</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>2048684330202</v>
+        <v>2048684330196</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>2048684330240</v>
+        <v>2048684330202</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>2048684330271</v>
+        <v>2048684330240</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -545,15 +545,15 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>2048684330691</v>
+        <v>2048684330271</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>2048684330721</v>
+        <v>2048684330691</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -561,15 +561,15 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>2048684330752</v>
+        <v>2048684330721</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>2048684330776</v>
+        <v>2048684330752</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>2048684330806</v>
+        <v>2048684330776</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>2048684330844</v>
+        <v>2048684330806</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>2048684330899</v>
+        <v>2048684330844</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>2048684330943</v>
+        <v>2048684330899</v>
       </c>
       <c r="B26">
         <v>5</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>2048684330974</v>
+        <v>2048684330943</v>
       </c>
       <c r="B27">
         <v>5</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>2048684331018</v>
+        <v>2048684330974</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>2048684331025</v>
+        <v>2048684331018</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>2048684331032</v>
+        <v>2048684331025</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>2048684331360</v>
+        <v>2048684331032</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -649,7 +649,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>2048684331391</v>
+        <v>2048684331360</v>
       </c>
       <c r="B32">
         <v>5</v>
@@ -657,7 +657,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>2048684331407</v>
+        <v>2048684331391</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>2048684331414</v>
+        <v>2048684331407</v>
       </c>
       <c r="B34">
         <v>5</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>2048684331421</v>
+        <v>2048684331414</v>
       </c>
       <c r="B35">
         <v>5</v>
@@ -681,23 +681,23 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>2048684331476</v>
+        <v>2048684331421</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>2048684331506</v>
+        <v>2048684331476</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>2048684331520</v>
+        <v>2048684331506</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>2048684331544</v>
+        <v>2048684331520</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>2048684331568</v>
+        <v>2048684331544</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>2048684331575</v>
+        <v>2048684331568</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2048684331605</v>
+        <v>2048684331575</v>
       </c>
       <c r="B42">
         <v>5</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>2048684331629</v>
+        <v>2048684331605</v>
       </c>
       <c r="B43">
         <v>5</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2048684331704</v>
+        <v>2048684331629</v>
       </c>
       <c r="B44">
         <v>5</v>
@@ -753,23 +753,23 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2048684331766</v>
+        <v>2048684331704</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2048684331827</v>
+        <v>2048684331766</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2048684331889</v>
+        <v>2048684331827</v>
       </c>
       <c r="B47">
         <v>5</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2048684331919</v>
+        <v>2048684331889</v>
       </c>
       <c r="B48">
         <v>5</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2048684331940</v>
+        <v>2048684331919</v>
       </c>
       <c r="B49">
         <v>5</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2048684331964</v>
+        <v>2048684331940</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2048684331988</v>
+        <v>2048684331964</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>2048684332008</v>
+        <v>2048684331988</v>
       </c>
       <c r="B52">
         <v>5</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>2048684332015</v>
+        <v>2048684332008</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>2048684332022</v>
+        <v>2048684332015</v>
       </c>
       <c r="B54">
         <v>5</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>2048684332046</v>
+        <v>2048684332022</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>2048684332060</v>
+        <v>2048684332046</v>
       </c>
       <c r="B56">
         <v>5</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>2048684332077</v>
+        <v>2048684332060</v>
       </c>
       <c r="B57">
         <v>5</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>2048684332091</v>
+        <v>2048684332077</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>2048684332114</v>
+        <v>2048684332091</v>
       </c>
       <c r="B59">
         <v>5</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>2048684332121</v>
+        <v>2048684332114</v>
       </c>
       <c r="B60">
         <v>5</v>
@@ -881,7 +881,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>2048684328476</v>
+        <v>2048684332121</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -889,15 +889,15 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>2048684328490</v>
+        <v>2048684328476</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>2048684328506</v>
+        <v>2048684328490</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -905,15 +905,15 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>2048684328513</v>
+        <v>2048684328506</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>2048684328520</v>
+        <v>2048684328513</v>
       </c>
       <c r="B65">
         <v>5</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>2048684328551</v>
+        <v>2048684328520</v>
       </c>
       <c r="B66">
         <v>5</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>2048684328568</v>
+        <v>2048684328551</v>
       </c>
       <c r="B67">
         <v>5</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>2048684328575</v>
+        <v>2048684328568</v>
       </c>
       <c r="B68">
         <v>5</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>2048684328582</v>
+        <v>2048684328575</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>2048684328605</v>
+        <v>2048684328582</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -961,23 +961,23 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>2048684328612</v>
+        <v>2048684328605</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>2048684328636</v>
+        <v>2048684328612</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>2048684328643</v>
+        <v>2048684328636</v>
       </c>
       <c r="B73">
         <v>5</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>2048684328650</v>
+        <v>2048684328643</v>
       </c>
       <c r="B74">
         <v>5</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>2048684328674</v>
+        <v>2048684328650</v>
       </c>
       <c r="B75">
         <v>5</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>2048684328698</v>
+        <v>2048684328674</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>2048684328728</v>
+        <v>2048684328698</v>
       </c>
       <c r="B77">
         <v>5</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>2048684328735</v>
+        <v>2048684328728</v>
       </c>
       <c r="B78">
         <v>5</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>2048684328759</v>
+        <v>2048684328735</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>2048684328773</v>
+        <v>2048684328759</v>
       </c>
       <c r="B80">
         <v>5</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>2048684328780</v>
+        <v>2048684328773</v>
       </c>
       <c r="B81">
         <v>5</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>2048684328803</v>
+        <v>2048684328780</v>
       </c>
       <c r="B82">
         <v>5</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>2048684328810</v>
+        <v>2048684328803</v>
       </c>
       <c r="B83">
         <v>5</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>2048684328834</v>
+        <v>2048684328810</v>
       </c>
       <c r="B84">
         <v>5</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>2048684328841</v>
+        <v>2048684328834</v>
       </c>
       <c r="B85">
         <v>5</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>2048684328858</v>
+        <v>2048684328841</v>
       </c>
       <c r="B86">
         <v>5</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>2048684328865</v>
+        <v>2048684328858</v>
       </c>
       <c r="B87">
         <v>5</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>2048684328872</v>
+        <v>2048684328865</v>
       </c>
       <c r="B88">
         <v>5</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>2048684328896</v>
+        <v>2048684328872</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>2048684328919</v>
+        <v>2048684328896</v>
       </c>
       <c r="B90">
         <v>5</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>2048684329183</v>
+        <v>2048684328919</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>2048684329190</v>
+        <v>2048684329183</v>
       </c>
       <c r="B92">
         <v>5</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>2048684329206</v>
+        <v>2048684329190</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>2048684329275</v>
+        <v>2048684329206</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>2048684329329</v>
+        <v>2048684329275</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>2048684329343</v>
+        <v>2048684329329</v>
       </c>
       <c r="B96">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>2048684329350</v>
+        <v>2048684329343</v>
       </c>
       <c r="B97">
         <v>5</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>2048684329374</v>
+        <v>2048684329350</v>
       </c>
       <c r="B98">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>2048684329411</v>
+        <v>2048684329374</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>2048684329459</v>
+        <v>2048684329411</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>2048684329497</v>
+        <v>2048684329459</v>
       </c>
       <c r="B101">
         <v>5</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>2048684329510</v>
+        <v>2048684329497</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>2048684329527</v>
+        <v>2048684329510</v>
       </c>
       <c r="B103">
         <v>5</v>
@@ -1225,23 +1225,23 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>2048684329541</v>
+        <v>2048684329527</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>2048684329558</v>
+        <v>2048684329541</v>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>2048729432823</v>
+        <v>2048684329558</v>
       </c>
       <c r="B106">
         <v>5</v>
@@ -1249,23 +1249,23 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>2048729432861</v>
+        <v>2048729432823</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>2048729432854</v>
+        <v>2048729432861</v>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>2048208983624</v>
+        <v>2048729432854</v>
       </c>
       <c r="B109">
         <v>5</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>2047914434871</v>
+        <v>2048208983624</v>
       </c>
       <c r="B110">
         <v>5</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>2047914434864</v>
+        <v>2047914434871</v>
       </c>
       <c r="B111">
         <v>5</v>
@@ -1289,15 +1289,15 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>2047914434819</v>
+        <v>2047914434864</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>2047914434727</v>
+        <v>2047914434819</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>2047914434697</v>
+        <v>2047914434727</v>
       </c>
       <c r="B114">
         <v>5</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>2047914434673</v>
+        <v>2047914434697</v>
       </c>
       <c r="B115">
         <v>5</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>2047914434833</v>
+        <v>2047914434673</v>
       </c>
       <c r="B116">
         <v>5</v>
@@ -1329,15 +1329,15 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>2047914434840</v>
+        <v>2047914434833</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>2047914434680</v>
+        <v>2047914434840</v>
       </c>
       <c r="B118">
         <v>5</v>
@@ -1345,15 +1345,15 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>2047914434895</v>
+        <v>2047914434680</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>2049626027266</v>
+        <v>2047914434895</v>
       </c>
       <c r="B120">
         <v>5</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>2047914434888</v>
+        <v>2049626027266</v>
       </c>
       <c r="B121">
         <v>5</v>
@@ -1369,15 +1369,15 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>2047914434758</v>
+        <v>2047914434888</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>2047914434765</v>
+        <v>2047914434758</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>2047914434772</v>
+        <v>2047914434765</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -1393,15 +1393,15 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>2047914434734</v>
+        <v>2047914434772</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>2049627411606</v>
+        <v>2047914434734</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,23 +1409,23 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>2048589156259</v>
+        <v>2049627411606</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>2048589156242</v>
+        <v>2048589156259</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>2048589156266</v>
+        <v>2048589156242</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>2047914434703</v>
+        <v>2048589156266</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -1441,15 +1441,15 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>2048589156273</v>
+        <v>2047914434703</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>2048208983662</v>
+        <v>2048589156273</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -1457,15 +1457,23 @@
     </row>
     <row r="133">
       <c r="A133">
+        <v>2048208983662</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
         <v>2048208983587</v>
       </c>
-      <c r="B133">
-        <v>5</v>
+      <c r="B134">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B134"/>
   </ignoredErrors>
 </worksheet>
 </file>